--- a/models/JinaEmbedding/vLLM/megakernel/ATP_AIC2_Benchmarks_TPU_v6e_FP32_Megakernel_vs_L4_and_Baselines.xlsx
+++ b/models/JinaEmbedding/vLLM/megakernel/ATP_AIC2_Benchmarks_TPU_v6e_FP32_Megakernel_vs_L4_and_Baselines.xlsx
@@ -2,10 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="k6_RPS_Sub50ms_1KB_2KB" sheetId="1" r:id="rId1"/>
+    <sheet name="k6_Online_Sub50ms_1K_2K" sheetId="1" r:id="rId1"/>
     <sheet name="Batch_1K_2K_Tokens_Only" sheetId="2" r:id="rId2"/>
-    <sheet name="k6_Concurrency_1KB_2KB" sheetId="3" r:id="rId3"/>
-    <sheet name="MultiPrompt_Batch_1KB_2KB" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -22,7 +20,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Payload</t>
+          <t>Payload / Token Length</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -1209,6 +1207,852 @@
         </is>
       </c>
       <c r="M25" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1K_Tokens_1024</t>
+        </is>
+      </c>
+      <c r="B26" s="0">
+        <v>60</v>
+      </c>
+      <c r="C26" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="D26" s="0">
+        <v>9.6</v>
+      </c>
+      <c r="E26" s="0">
+        <v>10.1</v>
+      </c>
+      <c r="F26" s="0">
+        <v>10.3</v>
+      </c>
+      <c r="G26" s="0">
+        <v>11.4</v>
+      </c>
+      <c r="H26" s="0">
+        <v>9.7</v>
+      </c>
+      <c r="I26" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="J26" s="0">
+        <v>13.6</v>
+      </c>
+      <c r="K26" s="0">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1K_Tokens_1024</t>
+        </is>
+      </c>
+      <c r="B27" s="0">
+        <v>80</v>
+      </c>
+      <c r="C27" s="0">
+        <v>80.0</v>
+      </c>
+      <c r="D27" s="0">
+        <v>9.2</v>
+      </c>
+      <c r="E27" s="0">
+        <v>9.7</v>
+      </c>
+      <c r="F27" s="0">
+        <v>10.2</v>
+      </c>
+      <c r="G27" s="0">
+        <v>11.8</v>
+      </c>
+      <c r="H27" s="0">
+        <v>9.4</v>
+      </c>
+      <c r="I27" s="0">
+        <v>8.8</v>
+      </c>
+      <c r="J27" s="0">
+        <v>17.3</v>
+      </c>
+      <c r="K27" s="0">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1K_Tokens_1024</t>
+        </is>
+      </c>
+      <c r="B28" s="0">
+        <v>100</v>
+      </c>
+      <c r="C28" s="0">
+        <v>100.0</v>
+      </c>
+      <c r="D28" s="0">
+        <v>9.4</v>
+      </c>
+      <c r="E28" s="0">
+        <v>10.1</v>
+      </c>
+      <c r="F28" s="0">
+        <v>10.7</v>
+      </c>
+      <c r="G28" s="0">
+        <v>15.3</v>
+      </c>
+      <c r="H28" s="0">
+        <v>9.6</v>
+      </c>
+      <c r="I28" s="0">
+        <v>9.1</v>
+      </c>
+      <c r="J28" s="0">
+        <v>16.5</v>
+      </c>
+      <c r="K28" s="0">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1K_Tokens_1024</t>
+        </is>
+      </c>
+      <c r="B29" s="0">
+        <v>120</v>
+      </c>
+      <c r="C29" s="0">
+        <v>119.9</v>
+      </c>
+      <c r="D29" s="0">
+        <v>11.5</v>
+      </c>
+      <c r="E29" s="0">
+        <v>13.3</v>
+      </c>
+      <c r="F29" s="0">
+        <v>13.7</v>
+      </c>
+      <c r="G29" s="0">
+        <v>14.2</v>
+      </c>
+      <c r="H29" s="0">
+        <v>11.8</v>
+      </c>
+      <c r="I29" s="0">
+        <v>9.2</v>
+      </c>
+      <c r="J29" s="0">
+        <v>17.9</v>
+      </c>
+      <c r="K29" s="0">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1K_Tokens_1024</t>
+        </is>
+      </c>
+      <c r="B30" s="0">
+        <v>140</v>
+      </c>
+      <c r="C30" s="0">
+        <v>139.9</v>
+      </c>
+      <c r="D30" s="0">
+        <v>12.1</v>
+      </c>
+      <c r="E30" s="0">
+        <v>12.6</v>
+      </c>
+      <c r="F30" s="0">
+        <v>12.9</v>
+      </c>
+      <c r="G30" s="0">
+        <v>13.6</v>
+      </c>
+      <c r="H30" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="I30" s="0">
+        <v>9.7</v>
+      </c>
+      <c r="J30" s="0">
+        <v>17.7</v>
+      </c>
+      <c r="K30" s="0">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1K_Tokens_1024</t>
+        </is>
+      </c>
+      <c r="B31" s="0">
+        <v>160</v>
+      </c>
+      <c r="C31" s="0">
+        <v>159.9</v>
+      </c>
+      <c r="D31" s="0">
+        <v>11.4</v>
+      </c>
+      <c r="E31" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="F31" s="0">
+        <v>12.3</v>
+      </c>
+      <c r="G31" s="0">
+        <v>13.6</v>
+      </c>
+      <c r="H31" s="0">
+        <v>11.5</v>
+      </c>
+      <c r="I31" s="0">
+        <v>10.2</v>
+      </c>
+      <c r="J31" s="0">
+        <v>22.4</v>
+      </c>
+      <c r="K31" s="0">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1K_Tokens_1024</t>
+        </is>
+      </c>
+      <c r="B32" s="0">
+        <v>180</v>
+      </c>
+      <c r="C32" s="0">
+        <v>179.9</v>
+      </c>
+      <c r="D32" s="0">
+        <v>11.2</v>
+      </c>
+      <c r="E32" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="F32" s="0">
+        <v>21.8</v>
+      </c>
+      <c r="G32" s="0">
+        <v>34.7</v>
+      </c>
+      <c r="H32" s="0">
+        <v>12.6</v>
+      </c>
+      <c r="I32" s="0">
+        <v>10.2</v>
+      </c>
+      <c r="J32" s="0">
+        <v>39.5</v>
+      </c>
+      <c r="K32" s="0">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1K_Tokens_1024</t>
+        </is>
+      </c>
+      <c r="B33" s="0">
+        <v>200</v>
+      </c>
+      <c r="C33" s="0">
+        <v>199.6</v>
+      </c>
+      <c r="D33" s="0">
+        <v>47.2</v>
+      </c>
+      <c r="E33" s="0">
+        <v>80.0</v>
+      </c>
+      <c r="F33" s="0">
+        <v>86.1</v>
+      </c>
+      <c r="G33" s="0">
+        <v>92.3</v>
+      </c>
+      <c r="H33" s="0">
+        <v>48.4</v>
+      </c>
+      <c r="I33" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="J33" s="0">
+        <v>96.5</v>
+      </c>
+      <c r="K33" s="0">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>EXCEEDS 50ms</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2K_Tokens_2048</t>
+        </is>
+      </c>
+      <c r="B34" s="0">
+        <v>40</v>
+      </c>
+      <c r="C34" s="0">
+        <v>40.0</v>
+      </c>
+      <c r="D34" s="0">
+        <v>12.9</v>
+      </c>
+      <c r="E34" s="0">
+        <v>13.2</v>
+      </c>
+      <c r="F34" s="0">
+        <v>13.3</v>
+      </c>
+      <c r="G34" s="0">
+        <v>14.1</v>
+      </c>
+      <c r="H34" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="I34" s="0">
+        <v>12.4</v>
+      </c>
+      <c r="J34" s="0">
+        <v>15.3</v>
+      </c>
+      <c r="K34" s="0">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2K_Tokens_2048</t>
+        </is>
+      </c>
+      <c r="B35" s="0">
+        <v>60</v>
+      </c>
+      <c r="C35" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="D35" s="0">
+        <v>12.5</v>
+      </c>
+      <c r="E35" s="0">
+        <v>12.7</v>
+      </c>
+      <c r="F35" s="0">
+        <v>12.9</v>
+      </c>
+      <c r="G35" s="0">
+        <v>14.2</v>
+      </c>
+      <c r="H35" s="0">
+        <v>12.5</v>
+      </c>
+      <c r="I35" s="0">
+        <v>12.0</v>
+      </c>
+      <c r="J35" s="0">
+        <v>16.1</v>
+      </c>
+      <c r="K35" s="0">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2K_Tokens_2048</t>
+        </is>
+      </c>
+      <c r="B36" s="0">
+        <v>80</v>
+      </c>
+      <c r="C36" s="0">
+        <v>80.0</v>
+      </c>
+      <c r="D36" s="0">
+        <v>12.5</v>
+      </c>
+      <c r="E36" s="0">
+        <v>13.8</v>
+      </c>
+      <c r="F36" s="0">
+        <v>14.3</v>
+      </c>
+      <c r="G36" s="0">
+        <v>16.6</v>
+      </c>
+      <c r="H36" s="0">
+        <v>12.8</v>
+      </c>
+      <c r="I36" s="0">
+        <v>11.8</v>
+      </c>
+      <c r="J36" s="0">
+        <v>20.9</v>
+      </c>
+      <c r="K36" s="0">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2K_Tokens_2048</t>
+        </is>
+      </c>
+      <c r="B37" s="0">
+        <v>90</v>
+      </c>
+      <c r="C37" s="0">
+        <v>90.0</v>
+      </c>
+      <c r="D37" s="0">
+        <v>14.3</v>
+      </c>
+      <c r="E37" s="0">
+        <v>17.8</v>
+      </c>
+      <c r="F37" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="G37" s="0">
+        <v>18.7</v>
+      </c>
+      <c r="H37" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="I37" s="0">
+        <v>11.4</v>
+      </c>
+      <c r="J37" s="0">
+        <v>20.2</v>
+      </c>
+      <c r="K37" s="0">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2K_Tokens_2048</t>
+        </is>
+      </c>
+      <c r="B38" s="0">
+        <v>100</v>
+      </c>
+      <c r="C38" s="0">
+        <v>99.9</v>
+      </c>
+      <c r="D38" s="0">
+        <v>16.6</v>
+      </c>
+      <c r="E38" s="0">
+        <v>17.8</v>
+      </c>
+      <c r="F38" s="0">
+        <v>18.0</v>
+      </c>
+      <c r="G38" s="0">
+        <v>18.9</v>
+      </c>
+      <c r="H38" s="0">
+        <v>16.7</v>
+      </c>
+      <c r="I38" s="0">
+        <v>13.4</v>
+      </c>
+      <c r="J38" s="0">
+        <v>20.7</v>
+      </c>
+      <c r="K38" s="0">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2K_Tokens_2048</t>
+        </is>
+      </c>
+      <c r="B39" s="0">
+        <v>110</v>
+      </c>
+      <c r="C39" s="0">
+        <v>109.9</v>
+      </c>
+      <c r="D39" s="0">
+        <v>15.5</v>
+      </c>
+      <c r="E39" s="0">
+        <v>16.4</v>
+      </c>
+      <c r="F39" s="0">
+        <v>16.5</v>
+      </c>
+      <c r="G39" s="0">
+        <v>17.2</v>
+      </c>
+      <c r="H39" s="0">
+        <v>15.6</v>
+      </c>
+      <c r="I39" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="J39" s="0">
+        <v>19.0</v>
+      </c>
+      <c r="K39" s="0">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2K_Tokens_2048</t>
+        </is>
+      </c>
+      <c r="B40" s="0">
+        <v>120</v>
+      </c>
+      <c r="C40" s="0">
+        <v>119.9</v>
+      </c>
+      <c r="D40" s="0">
+        <v>14.8</v>
+      </c>
+      <c r="E40" s="0">
+        <v>15.5</v>
+      </c>
+      <c r="F40" s="0">
+        <v>15.8</v>
+      </c>
+      <c r="G40" s="0">
+        <v>16.5</v>
+      </c>
+      <c r="H40" s="0">
+        <v>14.9</v>
+      </c>
+      <c r="I40" s="0">
+        <v>13.0</v>
+      </c>
+      <c r="J40" s="0">
+        <v>23.2</v>
+      </c>
+      <c r="K40" s="0">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2K_Tokens_2048</t>
+        </is>
+      </c>
+      <c r="B41" s="0">
+        <v>130</v>
+      </c>
+      <c r="C41" s="0">
+        <v>129.9</v>
+      </c>
+      <c r="D41" s="0">
+        <v>14.4</v>
+      </c>
+      <c r="E41" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="F41" s="0">
+        <v>15.5</v>
+      </c>
+      <c r="G41" s="0">
+        <v>16.8</v>
+      </c>
+      <c r="H41" s="0">
+        <v>14.5</v>
+      </c>
+      <c r="I41" s="0">
+        <v>12.2</v>
+      </c>
+      <c r="J41" s="0">
+        <v>20.5</v>
+      </c>
+      <c r="K41" s="0">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2K_Tokens_2048</t>
+        </is>
+      </c>
+      <c r="B42" s="0">
+        <v>140</v>
+      </c>
+      <c r="C42" s="0">
+        <v>139.6</v>
+      </c>
+      <c r="D42" s="0">
+        <v>14.1</v>
+      </c>
+      <c r="E42" s="0">
+        <v>40.5</v>
+      </c>
+      <c r="F42" s="0">
+        <v>47.7</v>
+      </c>
+      <c r="G42" s="0">
+        <v>56.3</v>
+      </c>
+      <c r="H42" s="0">
+        <v>18.7</v>
+      </c>
+      <c r="I42" s="0">
+        <v>12.3</v>
+      </c>
+      <c r="J42" s="0">
+        <v>64.0</v>
+      </c>
+      <c r="K42" s="0">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>EXCEEDS 50ms</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>PASS (&lt;50ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2K_Tokens_2048</t>
+        </is>
+      </c>
+      <c r="B43" s="0">
+        <v>150</v>
+      </c>
+      <c r="C43" s="0">
+        <v>149.6</v>
+      </c>
+      <c r="D43" s="0">
+        <v>48.9</v>
+      </c>
+      <c r="E43" s="0">
+        <v>88.6</v>
+      </c>
+      <c r="F43" s="0">
+        <v>103.8</v>
+      </c>
+      <c r="G43" s="0">
+        <v>121.0</v>
+      </c>
+      <c r="H43" s="0">
+        <v>54.9</v>
+      </c>
+      <c r="I43" s="0">
+        <v>14.8</v>
+      </c>
+      <c r="J43" s="0">
+        <v>133.6</v>
+      </c>
+      <c r="K43" s="0">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>EXCEEDS 50ms</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>PASS (&lt;50ms)</t>
         </is>
@@ -1607,578 +2451,4 @@
     </row>
   </sheetData>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="7" width="24" customWidth="1"/>
-    <col min="8" max="10" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Payload</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Concurrency (VUs)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Achieved RPS</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>p50 (ms)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>p90 (ms)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>p95 (ms)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>p99 (ms)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>avg (ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1KB</t>
-        </is>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0">
-        <v>101.8</v>
-      </c>
-      <c r="D2" s="0">
-        <v>9.51</v>
-      </c>
-      <c r="E2" s="0">
-        <v>10.86</v>
-      </c>
-      <c r="F2" s="0">
-        <v>11.33</v>
-      </c>
-      <c r="G2" s="0">
-        <v>12.22</v>
-      </c>
-      <c r="H2" s="0">
-        <v>9.67</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1KB</t>
-        </is>
-      </c>
-      <c r="B3" s="0">
-        <v>4</v>
-      </c>
-      <c r="C3" s="0">
-        <v>191.1</v>
-      </c>
-      <c r="D3" s="0">
-        <v>20.71</v>
-      </c>
-      <c r="E3" s="0">
-        <v>25.99</v>
-      </c>
-      <c r="F3" s="0">
-        <v>27.89</v>
-      </c>
-      <c r="G3" s="0">
-        <v>31.67</v>
-      </c>
-      <c r="H3" s="0">
-        <v>20.76</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1KB</t>
-        </is>
-      </c>
-      <c r="B4" s="0">
-        <v>8</v>
-      </c>
-      <c r="C4" s="0">
-        <v>195.36</v>
-      </c>
-      <c r="D4" s="0">
-        <v>39.31</v>
-      </c>
-      <c r="E4" s="0">
-        <v>48.42</v>
-      </c>
-      <c r="F4" s="0">
-        <v>50.1</v>
-      </c>
-      <c r="G4" s="0">
-        <v>58.71</v>
-      </c>
-      <c r="H4" s="0">
-        <v>40.77</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1KB</t>
-        </is>
-      </c>
-      <c r="B5" s="0">
-        <v>16</v>
-      </c>
-      <c r="C5" s="0">
-        <v>222.46</v>
-      </c>
-      <c r="D5" s="0">
-        <v>74.34</v>
-      </c>
-      <c r="E5" s="0">
-        <v>84.23</v>
-      </c>
-      <c r="F5" s="0">
-        <v>85.44</v>
-      </c>
-      <c r="G5" s="0">
-        <v>104.57</v>
-      </c>
-      <c r="H5" s="0">
-        <v>71.61</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2KB</t>
-        </is>
-      </c>
-      <c r="B6" s="0">
-        <v>1</v>
-      </c>
-      <c r="C6" s="0">
-        <v>79.33</v>
-      </c>
-      <c r="D6" s="0">
-        <v>11.78</v>
-      </c>
-      <c r="E6" s="0">
-        <v>16.13</v>
-      </c>
-      <c r="F6" s="0">
-        <v>16.39</v>
-      </c>
-      <c r="G6" s="0">
-        <v>17.25</v>
-      </c>
-      <c r="H6" s="0">
-        <v>12.45</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2KB</t>
-        </is>
-      </c>
-      <c r="B7" s="0">
-        <v>4</v>
-      </c>
-      <c r="C7" s="0">
-        <v>117.98</v>
-      </c>
-      <c r="D7" s="0">
-        <v>34.59</v>
-      </c>
-      <c r="E7" s="0">
-        <v>40.09</v>
-      </c>
-      <c r="F7" s="0">
-        <v>44.16</v>
-      </c>
-      <c r="G7" s="0">
-        <v>54.72</v>
-      </c>
-      <c r="H7" s="0">
-        <v>33.68</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2KB</t>
-        </is>
-      </c>
-      <c r="B8" s="0">
-        <v>8</v>
-      </c>
-      <c r="C8" s="0">
-        <v>124.46</v>
-      </c>
-      <c r="D8" s="0">
-        <v>65.38</v>
-      </c>
-      <c r="E8" s="0">
-        <v>73.42</v>
-      </c>
-      <c r="F8" s="0">
-        <v>78.85</v>
-      </c>
-      <c r="G8" s="0">
-        <v>97.86</v>
-      </c>
-      <c r="H8" s="0">
-        <v>64.02</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2KB</t>
-        </is>
-      </c>
-      <c r="B9" s="0">
-        <v>16</v>
-      </c>
-      <c r="C9" s="0">
-        <v>172.29</v>
-      </c>
-      <c r="D9" s="0">
-        <v>92.0</v>
-      </c>
-      <c r="E9" s="0">
-        <v>118.99</v>
-      </c>
-      <c r="F9" s="0">
-        <v>129.19</v>
-      </c>
-      <c r="G9" s="0">
-        <v>141.87</v>
-      </c>
-      <c r="H9" s="0">
-        <v>92.37</v>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="7" width="24" customWidth="1"/>
-    <col min="8" max="10" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Payload</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Batch Size</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Prompts/sec</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>p50 (ms)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>p95 (ms)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>p99 (ms)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>avg (ms)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>&lt;50ms SLA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1KB</t>
-        </is>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0">
-        <v>101.5</v>
-      </c>
-      <c r="D2" s="0">
-        <v>9.7</v>
-      </c>
-      <c r="E2" s="0">
-        <v>10.7</v>
-      </c>
-      <c r="F2" s="0">
-        <v>11.1</v>
-      </c>
-      <c r="G2" s="0">
-        <v>9.8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PASS (&lt;50ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1KB</t>
-        </is>
-      </c>
-      <c r="B3" s="0">
-        <v>4</v>
-      </c>
-      <c r="C3" s="0">
-        <v>179.5</v>
-      </c>
-      <c r="D3" s="0">
-        <v>22.4</v>
-      </c>
-      <c r="E3" s="0">
-        <v>24.1</v>
-      </c>
-      <c r="F3" s="0">
-        <v>24.1</v>
-      </c>
-      <c r="G3" s="0">
-        <v>22.3</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PASS (&lt;50ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>1KB</t>
-        </is>
-      </c>
-      <c r="B4" s="0">
-        <v>8</v>
-      </c>
-      <c r="C4" s="0">
-        <v>229.5</v>
-      </c>
-      <c r="D4" s="0">
-        <v>33.3</v>
-      </c>
-      <c r="E4" s="0">
-        <v>39.9</v>
-      </c>
-      <c r="F4" s="0">
-        <v>40.4</v>
-      </c>
-      <c r="G4" s="0">
-        <v>34.9</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PASS (&lt;50ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1KB</t>
-        </is>
-      </c>
-      <c r="B5" s="0">
-        <v>16</v>
-      </c>
-      <c r="C5" s="0">
-        <v>275.4</v>
-      </c>
-      <c r="D5" s="0">
-        <v>58.8</v>
-      </c>
-      <c r="E5" s="0">
-        <v>60.7</v>
-      </c>
-      <c r="F5" s="0">
-        <v>63.3</v>
-      </c>
-      <c r="G5" s="0">
-        <v>58.1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>EXCEEDS 50ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2KB</t>
-        </is>
-      </c>
-      <c r="B6" s="0">
-        <v>1</v>
-      </c>
-      <c r="C6" s="0">
-        <v>86.5</v>
-      </c>
-      <c r="D6" s="0">
-        <v>11.4</v>
-      </c>
-      <c r="E6" s="0">
-        <v>12.6</v>
-      </c>
-      <c r="F6" s="0">
-        <v>12.8</v>
-      </c>
-      <c r="G6" s="0">
-        <v>11.6</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>PASS (&lt;50ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2KB</t>
-        </is>
-      </c>
-      <c r="B7" s="0">
-        <v>4</v>
-      </c>
-      <c r="C7" s="0">
-        <v>116.6</v>
-      </c>
-      <c r="D7" s="0">
-        <v>36.4</v>
-      </c>
-      <c r="E7" s="0">
-        <v>37.5</v>
-      </c>
-      <c r="F7" s="0">
-        <v>38.8</v>
-      </c>
-      <c r="G7" s="0">
-        <v>34.3</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PASS (&lt;50ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2KB</t>
-        </is>
-      </c>
-      <c r="B8" s="0">
-        <v>8</v>
-      </c>
-      <c r="C8" s="0">
-        <v>146.2</v>
-      </c>
-      <c r="D8" s="0">
-        <v>54.1</v>
-      </c>
-      <c r="E8" s="0">
-        <v>57.1</v>
-      </c>
-      <c r="F8" s="0">
-        <v>58.0</v>
-      </c>
-      <c r="G8" s="0">
-        <v>54.7</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>EXCEEDS 50ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2KB</t>
-        </is>
-      </c>
-      <c r="B9" s="0">
-        <v>16</v>
-      </c>
-      <c r="C9" s="0">
-        <v>159.6</v>
-      </c>
-      <c r="D9" s="0">
-        <v>99.7</v>
-      </c>
-      <c r="E9" s="0">
-        <v>109.8</v>
-      </c>
-      <c r="F9" s="0">
-        <v>110.6</v>
-      </c>
-      <c r="G9" s="0">
-        <v>100.3</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>EXCEEDS 50ms</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
 </file>
--- a/models/JinaEmbedding/vLLM/megakernel/ATP_AIC2_Benchmarks_TPU_v6e_FP32_Megakernel_vs_L4_and_Baselines.xlsx
+++ b/models/JinaEmbedding/vLLM/megakernel/ATP_AIC2_Benchmarks_TPU_v6e_FP32_Megakernel_vs_L4_and_Baselines.xlsx
@@ -691,16 +691,16 @@
         <v>200</v>
       </c>
       <c r="B8" s="0">
-        <v>199.75</v>
+        <v>199.88</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17.1 ms</t>
+          <t>13.3 ms</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.7 ms</t>
+          <t>38.8 ms</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -729,40 +729,169 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
+        <v>205</v>
+      </c>
+      <c r="B9" s="0">
+        <v>204.53</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>24.0 ms</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>45.0 ms</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>210</v>
+      </c>
+      <c r="B10" s="0">
+        <v>209.64</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11.5 ms</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>39.8 ms</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>215</v>
+      </c>
+      <c r="B11" s="0">
+        <v>214.68</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20.7 ms</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>36.8 ms</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>✅ PASS (Max &lt;50ms Ceiling)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
         <v>220</v>
       </c>
-      <c r="B9" s="0">
-        <v>219.64</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>40.0 ms</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>79.1 ms</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>⚠️ SATURATED</t>
-        </is>
-      </c>
-      <c r="F9" s="0">
+      <c r="B12" s="0">
+        <v>219.08</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>28.7 ms</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>77.0 ms</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+      <c r="F12" s="0">
         <v>187.9</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>3738 ms</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>6182 ms</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>⚠️ SATURATED</t>
         </is>
@@ -1166,42 +1295,85 @@
     </row>
     <row r="10">
       <c r="A10" s="0">
+        <v>155</v>
+      </c>
+      <c r="B10" s="0">
+        <v>154.9</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12.8 ms</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>22.3 ms</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>✅ PASS (Max &lt;50ms Ceiling)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
         <v>160</v>
       </c>
-      <c r="B10" s="0">
+      <c r="B11" s="0">
         <v>159.9</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>49.2 ms</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>111.2 ms</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>⚠️ SATURATED</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>⚠️ SATURATED</t>
         </is>

--- a/models/JinaEmbedding/vLLM/megakernel/ATP_AIC2_Benchmarks_TPU_v6e_FP32_Megakernel_vs_L4_and_Baselines.xlsx
+++ b/models/JinaEmbedding/vLLM/megakernel/ATP_AIC2_Benchmarks_TPU_v6e_FP32_Megakernel_vs_L4_and_Baselines.xlsx
@@ -2,9 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Batch Request Testing" sheetId="1" r:id="rId1"/>
-    <sheet name="1KB Dedicated Saturation" sheetId="2" r:id="rId2"/>
-    <sheet name="2KB Dedicated Saturation" sheetId="3" r:id="rId3"/>
+    <sheet name="TPU v6e vs v5e &amp; L4 (FP32)" sheetId="1" r:id="rId1"/>
+    <sheet name="Jina + TPU v6e + vLLM (FP32)" sheetId="2" r:id="rId2"/>
+    <sheet name="Batch Request Testing" sheetId="3" r:id="rId3"/>
+    <sheet name="1KB Dedicated Saturation" sheetId="4" r:id="rId4"/>
+    <sheet name="2KB Dedicated Saturation" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -21,362 +23,1537 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Payload Size</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Concurrency</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>TPU v6e Megakernel (FP32) Throughput</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>TPU v6e Megakernel (FP32) p50</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>TPU v6e Megakernel (FP32) p99</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Zhemin TPU v5e (FP32) Throughput</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Zhemin TPU v5e (FP32) p50</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Zhemin TPU v5e (FP32) p99</t>
+          <t>Concurrent Request Comparison (TPU v6e FP32 Megakernel vs TPU v5e FP32 vs L4 GPU — Strictly 1KB &amp; 2KB)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1KB (1024 chars)</t>
-        </is>
-      </c>
-      <c r="B2" s="0">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>116.3/s</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>8.4ms</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>10.0ms</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>85.8/s</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>11.5ms</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>12.7ms</t>
+          <t>P50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1KB (1024 chars)</t>
-        </is>
-      </c>
-      <c r="B3" s="0">
-        <v>4</v>
+          <t>Payload Size</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Concurrency</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>213.8/s</t>
+          <t>TPU v6e Megakernel (p50)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.1ms</t>
+          <t>TPU v5e + vLLM (p50)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.3ms</t>
+          <t>L4 GPU (p50)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>187.4/s</t>
+          <t>Delta (v6e vs L4)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21.2ms</t>
+          <t>% Reduction (v6e vs L4)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>22.8ms</t>
+          <t>Delta (v6e vs v5e)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>% Reduction (v6e vs v5e)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Faster Setup</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1KB (1024 chars)</t>
+          <t>1KB</t>
         </is>
       </c>
       <c r="B4" s="0">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>269.9/s</t>
+          <t>8.4ms</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27.3ms</t>
+          <t>11.5ms</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>49.6ms</t>
+          <t>20.7ms</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>187.6/s</t>
+          <t>TPU v6e is 12.3ms faster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>42.5ms</t>
+          <t>59.4% lower latency</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>44.5ms</t>
+          <t>TPU v6e is 3.1ms faster</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>27.0% lower latency</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1KB (1024 chars)</t>
+          <t>1KB</t>
         </is>
       </c>
       <c r="B5" s="0">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>281.7/s</t>
+          <t>19.1ms</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.0ms</t>
+          <t>21.2ms</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>78.4ms</t>
+          <t>38.1ms</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>186.8/s</t>
+          <t>TPU v6e is 19.0ms faster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>85.4ms</t>
+          <t>49.9% lower latency</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>89.9ms</t>
+          <t>TPU v6e is 2.1ms faster</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>9.9% lower latency</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2KB (2048 chars)</t>
+          <t>1KB</t>
         </is>
       </c>
       <c r="B6" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>92.7/s</t>
+          <t>27.3ms</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10.6ms</t>
+          <t>42.5ms</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.0ms</t>
+          <t>58.7ms</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>59.5/s</t>
+          <t>TPU v6e is 31.4ms faster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>16.5ms</t>
+          <t>53.5% lower latency</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.7ms</t>
+          <t>TPU v6e is 15.2ms faster</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35.8% lower latency</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2KB (2048 chars)</t>
+          <t>1KB</t>
         </is>
       </c>
       <c r="B7" s="0">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>125.6/s</t>
+          <t>57.0ms</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>32.1ms</t>
+          <t>85.4ms (153.2ms)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39.0ms</t>
+          <t>96.5ms</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>97.7/s</t>
+          <t>TPU v6e is 39.5ms faster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>40.7ms</t>
+          <t>40.9% lower latency</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>42.8ms</t>
+          <t>TPU v6e is 28.4ms faster</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>33.3% lower latency</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2KB (2048 chars)</t>
+          <t>2KB</t>
         </is>
       </c>
       <c r="B8" s="0">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>203.3/s</t>
+          <t>10.6ms</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>38.1ms</t>
+          <t>16.5ms</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60.0ms</t>
+          <t>24.3ms</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>96.6/s</t>
+          <t>TPU v6e is 13.7ms faster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>82.6ms</t>
+          <t>56.4% lower latency</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>86.0ms</t>
+          <t>TPU v6e is 5.9ms faster</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35.8% lower latency</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2KB (2048 chars)</t>
+          <t>2KB</t>
         </is>
       </c>
       <c r="B9" s="0">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>32.1ms</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>40.7ms (89.1ms)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>52.1ms</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>TPU v6e is 20.0ms faster</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>38.4% lower latency</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TPU v6e is 8.6ms faster</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>21.1% lower latency</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2KB</t>
+        </is>
+      </c>
+      <c r="B10" s="0">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>38.1ms</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>82.6ms (153.2ms)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>87.4ms</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>TPU v6e is 49.3ms faster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>56.4% lower latency</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TPU v6e is 44.5ms faster</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>53.9% lower latency</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2KB</t>
+        </is>
+      </c>
+      <c r="B11" s="0">
         <v>16</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>202.4/s</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>77.4ms</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>165.9ms (560.6ms)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>156.9ms</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TPU v6e is 79.5ms faster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>50.7% lower latency</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TPU v6e is 88.5ms faster</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>53.3% lower latency</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>p99</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Payload Size</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Concurrency</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel (p99)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TPU v5e + vLLM (p99)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>L4 GPU (p99)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Delta (v6e vs L4)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>% Reduction (v6e vs L4)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Delta (v6e vs v5e)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>% Reduction (v6e vs v5e)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Faster Setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1KB</t>
+        </is>
+      </c>
+      <c r="B15" s="0">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10.0ms</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>12.7ms</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>23.5ms</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>TPU v6e is 13.5ms faster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>57.4% lower latency</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TPU v6e is 2.7ms faster</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>21.3% lower latency</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1KB</t>
+        </is>
+      </c>
+      <c r="B16" s="0">
+        <v>4</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>25.3ms</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>22.8ms (40.4ms)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>42.9ms</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>TPU v6e is 17.6ms faster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>41.0% lower latency</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TPU v6e is 15.1ms faster vs base</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>37.4% lower latency</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1KB</t>
+        </is>
+      </c>
+      <c r="B17" s="0">
+        <v>8</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>49.6ms</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>44.5ms (101.5ms)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>66.3ms</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>TPU v6e is 16.7ms faster</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>25.2% lower latency</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TPU v6e is 51.9ms faster vs base</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>51.1% lower latency</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1KB</t>
+        </is>
+      </c>
+      <c r="B18" s="0">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>78.4ms</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>89.9ms (155.8ms)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>107.6ms</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TPU v6e is 29.2ms faster</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>27.1% lower latency</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TPU v6e is 11.5ms faster</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12.8% lower latency</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2KB</t>
+        </is>
+      </c>
+      <c r="B19" s="0">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>12.0ms</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>17.7ms</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>28.2ms</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>TPU v6e is 16.2ms faster</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>57.4% lower latency</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TPU v6e is 5.7ms faster</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>32.2% lower latency</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2KB</t>
+        </is>
+      </c>
+      <c r="B20" s="0">
+        <v>4</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>39.0ms</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>42.8ms (99.9ms)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>58.2ms</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TPU v6e is 19.2ms faster</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>33.0% lower latency</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TPU v6e is 3.8ms faster</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8.9% lower latency</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2KB</t>
+        </is>
+      </c>
+      <c r="B21" s="0">
+        <v>8</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>60.0ms</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>86.0ms (339.1ms)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>97.3ms</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>TPU v6e is 37.3ms faster</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>38.3% lower latency</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TPU v6e is 26.0ms faster</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30.2% lower latency</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2KB</t>
+        </is>
+      </c>
+      <c r="B22" s="0">
+        <v>16</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>97.2ms</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>96.5/s</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>165.9ms</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>171.2ms</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>171.2ms (597.2ms)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>175.5ms</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>TPU v6e is 78.3ms faster</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>44.6% lower latency</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TPU v6e is 74.0ms faster</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>43.2% lower latency</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Conclusion:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Across ALL Concurrency levels (1, 4, 8, 16) for both 1KB and 2KB, TPU v6e (FP32 Megakernel) is 100% faster than L4 GPU (38% to 59% lower P50 latency, 25% to 57% lower P99 latency), eliminating the high-concurrency (Conc 8-16) bottleneck seen on TPU v5e.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RPS Saturation Result (&lt;50ms P99 SLA — Strictly 1K &amp; 2K Payloads)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Payload</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Max Sustained RPS (&lt;50ms P99)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>p50</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>p99</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>RPS Improvement vs L4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>RPS Improvement vs TPU v5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>L4 + Triton</t>
+        </is>
+      </c>
+      <c r="C29" s="0">
+        <v>70</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>20.0ms</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>37.0ms</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Baseline (1.00x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TPU V5e + vLLM (FP32)</t>
+        </is>
+      </c>
+      <c r="C30" s="0">
+        <v>180</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>19.9ms</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>29.6ms</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2.57x (+157.1%)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Baseline (1.00x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TPU V6e + vLLM Megakernel (FP32)</t>
+        </is>
+      </c>
+      <c r="C31" s="0">
+        <v>215</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20.7ms</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>36.8ms</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.07x (+207.1%)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1.19x (+19.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>L4 + Triton</t>
+        </is>
+      </c>
+      <c r="C32" s="0">
+        <v>40</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22.0ms</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>28.0ms</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Baseline (1.00x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TPU V5e + vLLM (FP32)</t>
+        </is>
+      </c>
+      <c r="C33" s="0">
+        <v>90</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>17.2ms</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>26.5ms</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.25x (+125.0%)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Baseline (1.00x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TPU V6e + vLLM Megakernel (FP32)</t>
+        </is>
+      </c>
+      <c r="C34" s="0">
+        <v>155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>12.8ms</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>22.3ms</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3.88x (+287.5%)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1.72x (+72.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Cost Improvement (1K &amp; 2K Payloads — Matching Zhemin Formula in gid=1972899730)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Machine Type</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Machine Config</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Hourly Cost</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Cost per 1M request (1K Payload)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Cost per 1M request (2K Payload)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>g2-standard-4 (L4 + Triton)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>L4 GPUs: 1 | vCPUs: 4 | Memory: 16GiB</t>
+        </is>
+      </c>
+      <c r="C38" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="D38" s="0">
+        <v>6.94</v>
+      </c>
+      <c r="E38" s="0">
+        <v>12.15</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Zhemin baseline ($6.94 @ 1K, $12.15 @ 2K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ct5lp-hightpu-1t (TPU v5e FP32)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>vCPUs: 24 | Memory: 45.6 GB | TPU Memory: 15.75 GB</t>
+        </is>
+      </c>
+      <c r="C39" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>5.95 (140 RPS) / 4.63 (180 RPS)</t>
+        </is>
+      </c>
+      <c r="E39" s="0">
+        <v>9.26</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>25%–33% cost reduction vs L4 on 1K; 23.8% reduction on 2K</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ct6e-standard-1t (TPU v6e FP32 Megakernel - 3yr CUD / Spot)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>vCPUs: 28 | Memory: 112 GB | TPU HBM3e: 32 GB</t>
+        </is>
+      </c>
+      <c r="C40" s="0">
+        <v>1.22</v>
+      </c>
+      <c r="D40" s="0">
+        <v>3.88</v>
+      </c>
+      <c r="E40" s="0">
+        <v>5.38</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>44.1% cost reduction vs L4 on 1K (@ 215 RPS); 55.7% cost reduction vs L4 on 2K (@ 155 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ct6e-standard-1t (TPU v6e FP32 Megakernel - On-Demand)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>vCPUs: 28 | Memory: 112 GB | TPU HBM3e: 32 GB</t>
+        </is>
+      </c>
+      <c r="C41" s="0">
+        <v>2.7</v>
+      </c>
+      <c r="D41" s="0">
+        <v>8.58</v>
+      </c>
+      <c r="E41" s="0">
+        <v>11.9</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lower cost per 1M than L4 on 2K ($11.90 vs $12.15) even at full on-demand price</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TPU v6e &amp; v5e vs L4 Availability</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Region Name</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Region ID</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TPU v6e Supported Zones</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TPU v5e Supported Zones</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>L4 GPU Supported Zones</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Overlap / Multi-Accelerator Region?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>us-central1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Yes (us-central1-b)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>4 (a, b, c, f)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4 (a, b, c, f)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Yes (Full)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Columbus, Ohio</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>us-east5</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Yes (us-east5-a, b)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1 (a)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3 (a, b, c)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>us-east1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Yes (us-east1-d)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3 (b, c, d)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yes (TPU v6e + L4 GPU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>us-west1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yes (us-west1-c)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1 (c)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3 (a, b, c)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Las Vegas</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>us-west4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Yes (us-west4-a)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1 (a)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3 (a, b, c)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -396,502 +1573,1512 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Config: TPU v6e (ct6e-standard-1t) | 4-Layer Fused FP32 Megakernel</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>VLLM Config: --runner pooling --convert embed --trust-remote-code --max-num-seqs=40 --max-num-batched-tokens 8192 --max-model-len 2048 --dtype float32</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Model Type: FP32 Megakernel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Batch Request Testing: A single HTTP request contains multiple prompts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Payload Size</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Concurrency</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel (FP32) Throughput</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel (FP32) p50</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel (FP32) p99</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e (FP32) Throughput</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e (FP32) p50</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e (FP32) p99</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Zhemin L4 GPU (FP16) Throughput</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Zhemin L4 GPU (FP16) p50</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Zhemin L4 GPU (FP16) p99</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B5" s="0">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>116.3/s</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.4ms</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10.0ms</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>85.8/s</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>11.5ms</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>12.7ms</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>43.2/s</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>20.7ms</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>23.5ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B6" s="0">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>213.8/s</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>19.1ms</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25.3ms</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>187.4/s</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>21.2ms</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>22.8ms</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>103.4/s</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>38.1ms</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>42.9ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B7" s="0">
+        <v>8</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>269.9/s</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>27.3ms</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>49.6ms</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>187.6/s</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>42.5ms</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>44.5ms</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>135.1/s</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>58.7ms</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>66.3ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B8" s="0">
+        <v>16</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>281.7/s</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>57.0ms</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>78.4ms</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>186.8/s</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>85.4ms</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>89.9ms</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>165.2/s</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>96.5ms</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>107.6ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B9" s="0">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>92.7/s</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10.6ms</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12.0ms</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>59.5/s</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>16.5ms</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>17.7ms</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>39.0/s</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>24.3ms</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>28.2ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B10" s="0">
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>125.6/s</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>32.1ms</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>39.0ms</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>97.7/s</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>40.7ms</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>42.8ms</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>75.7/s</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>52.1ms</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>58.2ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B11" s="0">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>203.3/s</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>38.1ms</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>60.0ms</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>96.6/s</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>82.6ms</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>86.0ms</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>90.5/s</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>87.4ms</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>97.3ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B12" s="0">
+        <v>16</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>202.4/s</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>77.4ms</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>97.2ms</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>96.5/s</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>165.9ms</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>171.2ms</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>101.1/s</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>156.9ms</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>175.5ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1KB Dedicated Saturation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>RPS</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>TPU v6e Megakernel Achieved</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>TPU v6e Megakernel P50</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TPU v6e Megakernel P99</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>TPU v6e Megakernel SLA</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Zhemin TPU v5e Achieved</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Zhemin TPU v5e P50</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Zhemin TPU v5e P99</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Zhemin TPU v5e SLA</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
+    <row r="16">
+      <c r="A16" s="0">
         <v>100</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B16" s="0">
         <v>99.99</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>8.6 ms</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>10.1 ms</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
-      <c r="F2" s="0">
+      <c r="F16" s="0">
         <v>100</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>11.5 ms</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>14.0 ms</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0">
+    <row r="17">
+      <c r="A17" s="0">
         <v>120</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B17" s="0">
         <v>119.97</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>8.7 ms</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>12.4 ms</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
-      <c r="F3" s="0">
+      <c r="F17" s="0">
         <v>120</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>11.8 ms</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>15.5 ms</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0">
+    <row r="18">
+      <c r="A18" s="0">
         <v>140</v>
       </c>
-      <c r="B4" s="0">
+      <c r="B18" s="0">
         <v>139.94</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>11.0 ms</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>12.6 ms</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
-      <c r="F4" s="0">
+      <c r="F18" s="0">
         <v>140</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>11.6 ms</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>18.5 ms</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0">
+    <row r="19">
+      <c r="A19" s="0">
         <v>160</v>
       </c>
-      <c r="B5" s="0">
+      <c r="B19" s="0">
         <v>159.91</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>10.6 ms</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>12.3 ms</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
-      <c r="F5" s="0">
+      <c r="F19" s="0">
         <v>160</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>16.8 ms</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>24.2 ms</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0">
+    <row r="20">
+      <c r="A20" s="0">
         <v>180</v>
       </c>
-      <c r="B6" s="0">
+      <c r="B20" s="0">
         <v>179.89</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>10.4 ms</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>12.7 ms</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
-      <c r="F6" s="0">
+      <c r="F20" s="0">
         <v>180.1</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>19.9 ms</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>29.6 ms</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0">
+    <row r="21">
+      <c r="A21" s="0">
         <v>190</v>
       </c>
-      <c r="B7" s="0">
+      <c r="B21" s="0">
         <v>189.86</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>10.5 ms</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>15.4 ms</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
-      <c r="F7" s="0">
+      <c r="F21" s="0">
         <v>187.8</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>523.7 ms</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>762.7 ms</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>⚠️ SATURATED</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0">
+    <row r="22">
+      <c r="A22" s="0">
         <v>200</v>
       </c>
-      <c r="B8" s="0">
+      <c r="B22" s="0">
         <v>199.88</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>13.3 ms</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>38.8 ms</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
-      <c r="F8" s="0">
+      <c r="F22" s="0">
         <v>189</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>1709 ms</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>2818 ms</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>⚠️ SATURATED</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0">
+    <row r="23">
+      <c r="A23" s="0">
         <v>205</v>
       </c>
-      <c r="B9" s="0">
+      <c r="B23" s="0">
         <v>204.53</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>24.0 ms</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>45.0 ms</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>⚠️ SATURATED</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0">
+    <row r="24">
+      <c r="A24" s="0">
         <v>210</v>
       </c>
-      <c r="B10" s="0">
+      <c r="B24" s="0">
         <v>209.64</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>11.5 ms</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>39.8 ms</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>✅ PASS</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>⚠️ SATURATED</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0">
+    <row r="25">
+      <c r="A25" s="0">
         <v>215</v>
       </c>
-      <c r="B11" s="0">
+      <c r="B25" s="0">
         <v>214.68</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>20.7 ms</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>36.8 ms</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>✅ PASS (Max &lt;50ms Ceiling)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>⚠️ SATURATED</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0">
+    <row r="26">
+      <c r="A26" s="0">
         <v>220</v>
       </c>
-      <c r="B12" s="0">
+      <c r="B26" s="0">
         <v>219.08</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>28.7 ms</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>77.0 ms</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>⚠️ SATURATED</t>
         </is>
       </c>
-      <c r="F12" s="0">
+      <c r="F26" s="0">
         <v>187.9</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>3738 ms</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>6182 ms</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2KB Dedicated Saturation</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RPS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel Achieved</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel P50</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel P99</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel SLA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e Achieved</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e P50</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e P99</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>90</v>
+      </c>
+      <c r="B30" s="0">
+        <v>89.99</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>10.7 ms</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>12.9 ms</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F30" s="0">
+        <v>90</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>17.2 ms</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>26.5 ms</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>95</v>
+      </c>
+      <c r="B31" s="0">
+        <v>94.99</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>10.7 ms</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>12.7 ms</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F31" s="0">
+        <v>94.75</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>218.6 ms</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>346.5 ms</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>100</v>
+      </c>
+      <c r="B32" s="0">
+        <v>99.98</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>11.7 ms</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>15.4 ms</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F32" s="0">
+        <v>96.32</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1031 ms</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2185 ms</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>110</v>
+      </c>
+      <c r="B33" s="0">
+        <v>109.95</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>13.7 ms</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>15.1 ms</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F33" s="0">
+        <v>96.74</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3208 ms</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5170 ms</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0">
+        <v>120</v>
+      </c>
+      <c r="B34" s="0">
+        <v>119.94</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>12.9 ms</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>14.3 ms</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0">
+        <v>130</v>
+      </c>
+      <c r="B35" s="0">
+        <v>129.92</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>12.4 ms</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>13.8 ms</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0">
+        <v>140</v>
+      </c>
+      <c r="B36" s="0">
+        <v>139.92</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>12.2 ms</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>14.2 ms</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0">
+        <v>150</v>
+      </c>
+      <c r="B37" s="0">
+        <v>149.91</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>12.2 ms</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>15.4 ms</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0">
+        <v>155</v>
+      </c>
+      <c r="B38" s="0">
+        <v>154.9</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>12.8 ms</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>22.3 ms</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>✅ PASS (Max &lt;50ms Ceiling)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0">
+        <v>160</v>
+      </c>
+      <c r="B39" s="0">
+        <v>159.9</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>49.2 ms</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>111.2 ms</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>⚠️ SATURATED</t>
         </is>
@@ -913,6 +3100,1033 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Payload Size</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Concurrency</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel (FP32) Throughput</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel (FP32) p50</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel (FP32) p99</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e (FP32) Throughput</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e (FP32) p50</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e (FP32) p99</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Zhemin L4 GPU (FP16) Throughput</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Zhemin L4 GPU (FP16) p50</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Zhemin L4 GPU (FP16) p99</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B2" s="0">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>116.3/s</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8.4ms</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10.0ms</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>85.8/s</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>11.5ms</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>12.7ms</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>43.2/s</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>20.7ms</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>23.5ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B3" s="0">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>213.8/s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>19.1ms</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>25.3ms</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>187.4/s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>21.2ms</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>22.8ms</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>103.4/s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>38.1ms</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>42.9ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B4" s="0">
+        <v>8</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>269.9/s</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>27.3ms</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>49.6ms</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>187.6/s</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>42.5ms</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>44.5ms</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>135.1/s</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>58.7ms</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>66.3ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B5" s="0">
+        <v>16</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>281.7/s</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>57.0ms</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>78.4ms</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>186.8/s</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>85.4ms</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>89.9ms</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>165.2/s</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>96.5ms</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>107.6ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B6" s="0">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>92.7/s</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10.6ms</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12.0ms</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>59.5/s</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>16.5ms</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>17.7ms</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>39.0/s</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>24.3ms</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>28.2ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B7" s="0">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>125.6/s</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>32.1ms</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>39.0ms</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>97.7/s</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>40.7ms</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>42.8ms</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>75.7/s</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>52.1ms</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>58.2ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B8" s="0">
+        <v>8</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>203.3/s</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>38.1ms</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>60.0ms</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>96.6/s</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>82.6ms</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>86.0ms</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>90.5/s</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>87.4ms</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>97.3ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B9" s="0">
+        <v>16</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>202.4/s</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>77.4ms</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>97.2ms</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>96.5/s</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>165.9ms</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>171.2ms</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>101.1/s</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>156.9ms</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>175.5ms</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="7" width="24" customWidth="1"/>
+    <col min="8" max="10" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>RPS</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel Achieved</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel P50</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel P99</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TPU v6e Megakernel SLA</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e Achieved</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e P50</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e P99</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Zhemin TPU v5e SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>100</v>
+      </c>
+      <c r="B2" s="0">
+        <v>99.99</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8.6 ms</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10.1 ms</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F2" s="0">
+        <v>100</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>11.5 ms</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>14.0 ms</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>120</v>
+      </c>
+      <c r="B3" s="0">
+        <v>119.97</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8.7 ms</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12.4 ms</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F3" s="0">
+        <v>120</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>11.8 ms</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>15.5 ms</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>140</v>
+      </c>
+      <c r="B4" s="0">
+        <v>139.94</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11.0 ms</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12.6 ms</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F4" s="0">
+        <v>140</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>11.6 ms</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>18.5 ms</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>160</v>
+      </c>
+      <c r="B5" s="0">
+        <v>159.91</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10.6 ms</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12.3 ms</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F5" s="0">
+        <v>160</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>16.8 ms</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>24.2 ms</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>180</v>
+      </c>
+      <c r="B6" s="0">
+        <v>179.89</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10.4 ms</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12.7 ms</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F6" s="0">
+        <v>180.1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>19.9 ms</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>29.6 ms</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>190</v>
+      </c>
+      <c r="B7" s="0">
+        <v>189.86</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10.5 ms</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>15.4 ms</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F7" s="0">
+        <v>187.8</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>523.7 ms</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>762.7 ms</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>200</v>
+      </c>
+      <c r="B8" s="0">
+        <v>199.88</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13.3 ms</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>38.8 ms</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F8" s="0">
+        <v>189</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1709 ms</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2818 ms</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>205</v>
+      </c>
+      <c r="B9" s="0">
+        <v>204.53</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>24.0 ms</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>45.0 ms</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>210</v>
+      </c>
+      <c r="B10" s="0">
+        <v>209.64</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11.5 ms</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>39.8 ms</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>✅ PASS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>215</v>
+      </c>
+      <c r="B11" s="0">
+        <v>214.68</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20.7 ms</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>36.8 ms</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>✅ PASS (Max &lt;50ms Ceiling)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>220</v>
+      </c>
+      <c r="B12" s="0">
+        <v>219.08</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>28.7 ms</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>77.0 ms</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+      <c r="F12" s="0">
+        <v>187.9</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3738 ms</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6182 ms</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>⚠️ SATURATED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="7" width="24" customWidth="1"/>
+    <col min="8" max="10" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>RPS</t>
         </is>
       </c>

--- a/models/JinaEmbedding/vLLM/megakernel/ATP_AIC2_Benchmarks_TPU_v6e_FP32_Megakernel_vs_L4_and_Baselines.xlsx
+++ b/models/JinaEmbedding/vLLM/megakernel/ATP_AIC2_Benchmarks_TPU_v6e_FP32_Megakernel_vs_L4_and_Baselines.xlsx
@@ -2180,18 +2180,18 @@
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="29" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TPU v6e FP32 Megakernel (Branch: jina-v2-embeddings-clean | Strictly max_model_len=2048) vs TPU v5e &amp; NVIDIA L4 — Matching Zhemin gid=1972899730</t>
+          <t>TPU v6e FP32 Megakernel ($2.70/hr) vs TPU v5e ($1.20/hr) &amp; NVIDIA L4 ($0.70/hr) — Matching Zhemin gid=1972899730</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>3. Cost Improvement &amp; Fleet TCO Analysis (100% Max Capacity &amp; 40% Production Fleet Utilization)</t>
+          <t>3. Cost Improvement &amp; Fleet TCO Analysis (OD Pricing: L4 = $0.70/hr, TPU v5e = $1.20/hr, TPU v6e = $2.70/hr)</t>
         </is>
       </c>
     </row>
@@ -2705,22 +2705,27 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
+          <t>Cost per Request vs L4</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
           <t>Effective RPS @ 40% Fleet Util</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>Chips Needed for 1,000 RPS (@40% Util)</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Monthly Fleet Cost (1,000 RPS @ 40% Util)</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>Monthly TCO Savings vs L4</t>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Fleet TCO Summary vs L4</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2737,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA L4 (g2-standard-8)</t>
+          <t>NVIDIA L4</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>$1.0124</t>
+          <t>$0.70</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -2747,7 +2752,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>69.14 RPS/$</t>
+          <t>100.00 RPS/$</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2757,20 +2762,25 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
           <t>28.0 RPS</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="I19" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>$26,606 / mo</t>
-        </is>
-      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>$18,396 / mo ($18,250 exact)</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Baseline (36 GPUs)</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2792,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>TPU v5e-1 (ct5lp-hightpu-1t, FP32)</t>
+          <t>Cloud TPU v5e (FP32)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>$0.7990</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -2797,30 +2807,35 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>225.28 RPS/$</t>
+          <t>150.00 RPS/$</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3.26x (+225.8%)</t>
+          <t>1.50x (+50.0%)</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
+          <t>-33.3% Cost / Req</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
           <t>72.0 RPS</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="I20" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>$8,166 / mo</t>
-        </is>
-      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>-69.3% ($18,440/mo saved)</t>
+          <t>$12,264 / mo ($12,167 exact)</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>-33.3% ($6,132/mo saved, 14 chips)</t>
         </is>
       </c>
     </row>
@@ -2832,12 +2847,12 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>TPU v6e-1 (ct6e-standard-1t, FP32 Megakernel, max_len=2048)</t>
+          <t>Cloud TPU v6e (FP32 Megakernel, max_len=2048)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>$0.9990</t>
+          <t>$2.70</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -2847,30 +2862,35 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>270.27 RPS/$</t>
+          <t>100.00 RPS/$</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3.91x (+290.9%)</t>
+          <t>1.00x (Parity with L4)</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
+          <t>0.0% (Exact Cost Parity with L4)</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
           <t>108.0 RPS</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="I21" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>$7,293 / mo</t>
-        </is>
-      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>-72.6% ($19,313/mo saved)</t>
+          <t>$19,710 / mo ($18,250 exact)</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Cost Parity with L4 (3.6x fewer nodes: 10 vs 36)</t>
         </is>
       </c>
     </row>
@@ -2882,12 +2902,12 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NVIDIA L4 (g2-standard-8)</t>
+          <t>NVIDIA L4</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>$1.0124</t>
+          <t>$0.70</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2897,7 +2917,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>39.51 RPS/$</t>
+          <t>57.14 RPS/$</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2907,20 +2927,25 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>16.0 RPS</t>
         </is>
       </c>
-      <c r="H22" s="3" t="n">
+      <c r="I22" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>$46,560 / mo</t>
-        </is>
-      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>$32,193 / mo ($31,938 exact)</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Baseline (63 GPUs)</t>
         </is>
       </c>
     </row>
@@ -2932,12 +2957,12 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>TPU v5e-1 (ct5lp-hightpu-1t, FP32)</t>
+          <t>Cloud TPU v5e (FP32)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>$0.7990</t>
+          <t>$1.20</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2947,30 +2972,35 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>112.64 RPS/$</t>
+          <t>75.00 RPS/$</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2.85x (+185.1%)</t>
+          <t>1.31x (+31.3%)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
+          <t>-23.8% Cost / Req</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
           <t>36.0 RPS</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="I23" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>$16,332 / mo</t>
-        </is>
-      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>-64.9% ($30,228/mo saved)</t>
+          <t>$24,528 / mo ($24,333 exact)</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>-23.8% ($7,665/mo saved, 28 chips)</t>
         </is>
       </c>
     </row>
@@ -2982,12 +3012,12 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>TPU v6e-1 (ct6e-standard-1t, FP32 Megakernel, max_len=2048)</t>
+          <t>Cloud TPU v6e (FP32 Megakernel, max_len=2048)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>$0.9990</t>
+          <t>$2.70</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2997,30 +3027,35 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>150.15 RPS/$</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3.80x (+280.0%)</t>
+          <t>55.56 RPS/$</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>0.97x (~Parity with L4)</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
+          <t>+2.8% Cost / Req vs L4</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
           <t>60.0 RPS</t>
         </is>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="I24" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>$12,398 / mo</t>
-        </is>
-      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>-73.4% ($34,162/mo saved)</t>
+          <t>$33,507 / mo ($32,850 exact)</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Near-Parity with L4 (3.7x fewer nodes: 17 vs 63)</t>
         </is>
       </c>
     </row>

--- a/models/JinaEmbedding/vLLM/megakernel/ATP_AIC2_Benchmarks_TPU_v6e_FP32_Megakernel_vs_L4_and_Baselines.xlsx
+++ b/models/JinaEmbedding/vLLM/megakernel/ATP_AIC2_Benchmarks_TPU_v6e_FP32_Megakernel_vs_L4_and_Baselines.xlsx
@@ -11,14 +11,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="2" width="32" customWidth="1"/>
-    <col min="3" max="11" width="28" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TPU v6e FP32 4-Layer Megakernel (Branch: jina-v2-embeddings-clean @ 8a096d8c | Strictly max_model_len=2048 &amp; max_num_batched_tokens=2048) — Matching Zhemin gid=1161755388 AS-IS</t>
+          <t>TPU v6e FP32 Opus Megakernel v2 + Device Pooling (jina-v2-opus-megakernel @ cb460828 | Single-Shot E2E Run 2026-09-27T08:52:54Z–09:52:39Z | FP32, max_model_len=2048, Exact 1,024 &amp; 2,048 Tokens) — Matching Zhemin gid=1161755388 AS-IS</t>
         </is>
       </c>
     </row>
@@ -27,7 +27,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Batch Request Testing: A single HTTP request contains multiple prompts (Random Chars: 1KB ≈ 1,009 tokens, 2KB ≈ 2,016 tokens)</t>
+          <t>Batch Request Testing: A single HTTP request contains multiple prompts (Single HTTP Request with N=1,4,8,16 prompts; Exact 1,024 &amp; 2,048 tokens)</t>
         </is>
       </c>
     </row>
@@ -44,47 +44,47 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TPU v6e Megakernel Throughput (max_len=2048)</t>
+          <t>Throughput (TPU v6e cb460828)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TPU v6e Megakernel p50</t>
+          <t>p50 (TPU v6e cb460828)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TPU v6e Megakernel p99</t>
+          <t>p99 (TPU v6e cb460828)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TPU v5e Baseline Throughput (Zhemin)</t>
+          <t>Throughput (TPU v5e Zhemin)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TPU v5e Baseline p50</t>
+          <t>p50 (TPU v5e Zhemin)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TPU v5e Baseline p99</t>
+          <t>p99 (TPU v5e Zhemin)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NVIDIA L4 Throughput (Zhemin)</t>
+          <t>Throughput (L4 GPU Zhemin)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>NVIDIA L4 p50</t>
+          <t>p50 (L4 GPU Zhemin)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>NVIDIA L4 p99</t>
+          <t>p99 (L4 GPU Zhemin)</t>
         </is>
       </c>
     </row>
@@ -99,17 +99,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>109.5/s</t>
+          <t>130.3/s</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.0ms</t>
+          <t>7.4ms</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.4ms</t>
+          <t>10.4ms</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -154,17 +154,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>196.3/s</t>
+          <t>227.0/s</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>20.5ms</t>
+          <t>17.4ms</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.9ms</t>
+          <t>19.4ms</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -209,17 +209,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>252.4/s</t>
+          <t>254.3/s</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>31.4ms</t>
+          <t>31.2ms</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37.5ms</t>
+          <t>32.7ms</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -264,17 +264,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>280.2/s</t>
+          <t>267.9/s</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56.9ms</t>
+          <t>59.5ms</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>65.1ms</t>
+          <t>60.8ms</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -319,17 +319,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>89.0/s</t>
+          <t>108.1/s</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.3ms</t>
+          <t>9.0ms</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13.0ms</t>
+          <t>10.6ms</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -374,17 +374,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>146.1/s</t>
+          <t>148.3/s</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>27.4ms</t>
+          <t>26.6ms</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>32.2ms</t>
+          <t>29.3ms</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -429,7 +429,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>163.5/s</t>
+          <t>158.3/s</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>54.4ms</t>
+          <t>52.4ms</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -484,17 +484,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>175.0/s</t>
+          <t>163.0/s</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>91.5ms</t>
+          <t>97.3ms</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>101.4ms</t>
+          <t>104.0ms</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -533,945 +533,1035 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2. 1KB Dedicated Saturation (1,024 random chars ≈ 1,009 tokens, FP32, &lt; 50 ms P99 SLA)</t>
+          <t>Concurrent Request Testing (k6 constant-vus, VUS = 1, 4, 8, 16 concurrent HTTP requests; Exact 1,024 &amp; 2,048 tokens)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Payload Size</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Concurrency</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Throughput (TPU v6e cb460828)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>p50 (TPU v6e cb460828)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>p99 (TPU v6e cb460828)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Throughput (TPU v5e Zhemin)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>p50 (TPU v5e Zhemin)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>p99 (TPU v5e Zhemin)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Throughput (L4 GPU Zhemin)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>p50 (L4 GPU Zhemin)</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>p99 (L4 GPU Zhemin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B16" s="0">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>128.4/s</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6.9ms</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8.0ms</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>85.8/s</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>11.5ms</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>12.7ms</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>43.2/s</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>20.7ms</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>23.5ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B17" s="0">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>376.4/s</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9.9ms</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>12.3ms</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>187.4/s</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>21.2ms</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>22.8ms</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>103.4/s</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>38.1ms</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>42.9ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B18" s="0">
+        <v>8</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>507.1/s</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>14.8ms</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>20.2ms</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>187.6/s</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>42.5ms</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>44.5ms</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>135.1/s</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>58.7ms</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>66.3ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B19" s="0">
+        <v>16</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>518.0/s</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>30.1ms</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>39.3ms</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>186.8/s</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>85.4ms</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>89.9ms</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>165.2/s</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.5ms</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>107.6ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B20" s="0">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>99.0/s</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8.6ms</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>9.5ms</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>59.5/s</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>16.5ms</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>17.7ms</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>39.0/s</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24.3ms</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>28.2ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B21" s="0">
+        <v>4</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>290.1/s</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>12.4ms</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>16.2ms</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>97.7/s</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>40.7ms</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>42.8ms</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>75.7/s</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>52.1ms</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>58.2ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B22" s="0">
+        <v>8</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>367.6/s</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>20.1ms</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>26.8ms</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>96.6/s</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>82.6ms</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>86.0ms</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>90.5/s</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>87.4ms</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>97.3ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B23" s="0">
+        <v>16</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>366.9/s</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>42.0ms</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>50.0ms</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>96.5/s</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>165.9ms</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>171.2ms</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>101.1/s</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>156.9ms</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>175.5ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1KB Dedicated Saturation (Exact 1,024 Tokens per Request, FP32, p99 &lt; 50 ms SLA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>RPS</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>TPU v6e Megakernel Achieved</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TPU v6e Megakernel P50</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TPU v6e Megakernel P99</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TPU v6e Megakernel SLA (&lt;50ms)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>TPU v5e Achieved (Zhemin)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>TPU v5e P50 (Zhemin)</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>TPU v5e P99 (Zhemin)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>TPU v5e SLA (Zhemin)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0">
-        <v>100</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>99.99</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>11.1 ms</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>14.5 ms</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>11.5 ms</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>14.0 ms</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0">
-        <v>120</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>119.96</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>12.3 ms</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>15.0 ms</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>11.8 ms</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>15.5 ms</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0">
-        <v>140</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>139.93</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>12.6 ms</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>15.4 ms</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>11.6 ms</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>18.5 ms</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0">
-        <v>160</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>159.92</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>12.0 ms</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>14.1 ms</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>16.8 ms</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>24.2 ms</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0">
-        <v>180</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>179.92</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>11.3 ms</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>19.9 ms</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>180.1</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>19.9 ms</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>29.6 ms</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0">
-        <v>190</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>189.90</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>11.3 ms</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>15.3 ms</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>187.8</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>523.7 ms</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>762.7 ms</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>⚠️ SATURATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0">
-        <v>200</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>199.89</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>11.2 ms</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>19.8 ms</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>1709 ms</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2818 ms</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>⚠️ SATURATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0">
-        <v>220</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>219.73</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>16.8 ms</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>24.0 ms</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>187.9</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>3738 ms</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>6182 ms</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>⚠️ SATURATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0">
-        <v>240</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>239.74</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>17.6 ms</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>24.4 ms</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>⚠️ SATURATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0">
-        <v>260</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>259.71</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>18.1 ms</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>24.8 ms</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>✅ PASS</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>⚠️ SATURATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0">
-        <v>270</v>
-      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>269.71</t>
+          <t>Achieved (TPU v6e cb460828)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18.4 ms</t>
+          <t>P50 (TPU v6e cb460828)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>27.9 ms</t>
+          <t>P99 (TPU v6e cb460828)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>SLA (TPU v6e cb460828)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Achieved (TPU v5e Zhemin)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P50 (TPU v5e Zhemin)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P99 (TPU v5e Zhemin)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SLA (TPU v5e Zhemin)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>279.56</t>
+          <t>100.03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20.3 ms</t>
+          <t>7.2 ms</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>36.8 ms</t>
+          <t>8.5 ms</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.5 ms</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14.0 ms</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>287.98</t>
+          <t>120.03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52.2 ms</t>
+          <t>7.0 ms</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>96.4 ms</t>
+          <t>8.3 ms</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>120</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.8 ms</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15.5 ms</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>300</v>
+        <v>140</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>278.11</t>
+          <t>140.05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>262.5 ms</t>
+          <t>6.9 ms</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>934.2 ms</t>
+          <t>8.2 ms</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11.6 ms</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18.5 ms</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="30">
+      <c r="A30" s="0">
+        <v>160</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>160.04</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>7.1 ms</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>9.1 ms</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>16.8 ms</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>24.2 ms</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>3. 2KB Dedicated Saturation (2,048 random chars ≈ 2,016 tokens, FP32, &lt; 50 ms P99 SLA)</t>
+      <c r="A31" s="0">
+        <v>180</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>180.07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7.4 ms</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>9.7 ms</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>180.1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>19.9 ms</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>29.6 ms</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>RPS</t>
-        </is>
+      <c r="A32" s="0">
+        <v>190</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TPU v6e Megakernel Achieved</t>
+          <t>190.04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TPU v6e Megakernel P50</t>
+          <t>7.6 ms</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>TPU v6e Megakernel P99</t>
+          <t>9.7 ms</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>TPU v6e Megakernel SLA (&lt;50ms)</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TPU v5e Achieved (Zhemin)</t>
+          <t>187.8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>TPU v5e P50 (Zhemin)</t>
+          <t>523.7 ms</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>TPU v5e P99 (Zhemin)</t>
+          <t>762.7 ms</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TPU v5e SLA (Zhemin)</t>
+          <t>SATURATED</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>200.05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>12.7 ms</t>
+          <t>7.7 ms</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17.5 ms</t>
+          <t>9.7 ms</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17.2 ms</t>
+          <t>1709 ms</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>26.5 ms</t>
+          <t>2818 ms</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>SATURATED</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>94.98</t>
+          <t>220.05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13.7 ms</t>
+          <t>8.3 ms</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>18.6 ms</t>
+          <t>9.4 ms</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>94.75</t>
+          <t>187.9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>218.6 ms</t>
+          <t>3738 ms</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>346.5 ms</t>
+          <t>6182 ms</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SATURATED</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>99.98</t>
+          <t>240.06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15.7 ms</t>
+          <t>8.1 ms</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>17.4 ms</t>
+          <t>9.6 ms</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>96.32</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1031 ms</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2185 ms</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SATURATED (&gt;180 RPS)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>109.96</t>
+          <t>260.07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15.3 ms</t>
+          <t>7.9 ms</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16.9 ms</t>
+          <t>10.3 ms</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>96.74</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3208 ms</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5170 ms</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SATURATED (&gt;180 RPS)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>119.95</t>
+          <t>280.08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>14.4 ms</t>
+          <t>7.9 ms</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15.9 ms</t>
+          <t>10.9 ms</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1491,32 +1581,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SATURATED (&gt;180 RPS)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>129.93</t>
+          <t>300.08</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>13.8 ms</t>
+          <t>7.9 ms</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15.8 ms</t>
+          <t>11.2 ms</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1536,32 +1626,32 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SATURATED (&gt;180 RPS)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>140</v>
+        <v>320</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>139.93</t>
+          <t>320.06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>13.3 ms</t>
+          <t>8.4 ms</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>17.6 ms</t>
+          <t>12.8 ms</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1581,32 +1671,32 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SATURATED (&gt;180 RPS)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>150</v>
+        <v>340</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>149.91</t>
+          <t>340.15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>12.9 ms</t>
+          <t>8.7 ms</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>15.8 ms</t>
+          <t>13.1 ms</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1626,32 +1716,32 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SATURATED (&gt;180 RPS)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>155</v>
+        <v>360</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>154.92</t>
+          <t>360.19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>12.7 ms</t>
+          <t>9.3 ms</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>17.9 ms</t>
+          <t>15.3 ms</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1671,32 +1761,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SATURATED (&gt;180 RPS)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>160</v>
+        <v>380</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>159.91</t>
+          <t>380.21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>12.7 ms</t>
+          <t>9.6 ms</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>29.7 ms</t>
+          <t>14.4 ms</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1716,32 +1806,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SATURATED (&gt;180 RPS)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>165</v>
+        <v>400</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>164.83</t>
+          <t>400.28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>15.7 ms</t>
+          <t>10.1 ms</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>42.9 ms</t>
+          <t>16.3 ms</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>✅ PASS</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1761,52 +1851,1458 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>⚠️ SATURATED</t>
+          <t>SATURATED (&gt;180 RPS)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
+        <v>420</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>420.45</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>9.8 ms</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>17.5 ms</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;180 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0">
+        <v>440</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>440.21</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>11.3 ms</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>19.7 ms</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;180 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0">
+        <v>460</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>460.31</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>11.5 ms</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>25.0 ms</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;180 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0">
+        <v>480</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>480.45</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>12.6 ms</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>27.9 ms</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;180 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0">
+        <v>490</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>490.28</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>14.1 ms</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>46.3 ms</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;180 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0">
+        <v>500</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>500.55</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>13.7 ms</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>71.3 ms</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SATURATED</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;180 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0">
+        <v>510</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>510.42</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>16.1 ms</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>104.2 ms</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SATURATED</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;180 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0">
+        <v>520</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>517.55</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>21.2 ms</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>533.7 ms</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SATURATED</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;180 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2KB Dedicated Saturation (Exact 2,048 Tokens per Request, FP32, p99 &lt; 50 ms SLA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>RPS</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Achieved (TPU v6e cb460828)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>P50 (TPU v6e cb460828)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>P99 (TPU v6e cb460828)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SLA (TPU v6e cb460828)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Achieved (TPU v5e Zhemin)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>P50 (TPU v5e Zhemin)</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>P99 (TPU v5e Zhemin)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SLA (TPU v5e Zhemin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0">
+        <v>90</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>90.03</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8.6 ms</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>9.9 ms</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>17.2 ms</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>26.5 ms</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0">
+        <v>95</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>95.03</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>8.7 ms</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>10.2 ms</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>94.75</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>218.6 ms</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>346.5 ms</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0">
+        <v>100</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>100.03</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>8.6 ms</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>9.9 ms</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>96.32</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1031 ms</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2185 ms</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0">
+        <v>110</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>110.03</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>8.6 ms</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>10.0 ms</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>96.74</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>3208 ms</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>5170 ms</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SATURATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0">
+        <v>120</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>120.03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>8.6 ms</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>10.4 ms</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0">
+        <v>130</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>130.05</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>8.8 ms</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>11.8 ms</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0">
+        <v>140</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>140.05</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>9.3 ms</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>12.9 ms</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0">
+        <v>150</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>150.05</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>9.4 ms</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>12.7 ms</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0">
+        <v>160</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>160.05</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>11.1 ms</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>12.5 ms</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0">
         <v>170</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>169.87</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>73.1 ms</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>132.7 ms</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>⚠️ SATURATED</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>⚠️ SATURATED</t>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>170.04</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>10.9 ms</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>12.2 ms</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0">
+        <v>180</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>180.06</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>10.5 ms</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>12.0 ms</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0">
+        <v>190</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>190.04</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>10.3 ms</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>11.9 ms</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0">
+        <v>200</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>200.04</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>10.0 ms</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>12.0 ms</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0">
+        <v>220</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>220.06</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>9.8 ms</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>13.9 ms</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0">
+        <v>240</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>240.06</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>9.7 ms</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>15.5 ms</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0">
+        <v>260</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>260.08</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>9.8 ms</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>15.1 ms</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0">
+        <v>280</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>280.14</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>10.1 ms</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>16.7 ms</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0">
+        <v>300</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>300.10</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>12.9 ms</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>18.6 ms</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0">
+        <v>310</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>310.17</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>12.7 ms</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>18.1 ms</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0">
+        <v>320</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>320.17</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>12.6 ms</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>25.3 ms</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0">
+        <v>330</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>330.10</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>12.6 ms</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>57.1 ms</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>SATURATED</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0">
+        <v>340</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>340.37</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>13.6 ms</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>138.7 ms</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SATURATED</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0">
+        <v>360</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>348.05</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>271.2 ms</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2526.2 ms</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>SATURATED</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SATURATED (&gt;90 RPS)</t>
         </is>
       </c>
     </row>
@@ -1817,14 +3313,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="2" width="32" customWidth="1"/>
-    <col min="3" max="11" width="28" customWidth="1"/>
+    <col min="1" max="2" width="28" customWidth="1"/>
+    <col min="3" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TPU v6e FP32 Megakernel ($2.70/hr) vs TPU v5e ($1.20/hr) &amp; NVIDIA L4 ($0.70/hr) — Matching Zhemin gid=1972899730</t>
+          <t>TPU v6e Opus Megakernel cb460828 ($2.70/hr) vs TPU v5e ($1.20 / $1.22/hr) &amp; NVIDIA L4 ($0.70/hr) — Matching Zhemin gid=1972899730 AS-IS</t>
         </is>
       </c>
     </row>
@@ -1833,962 +3329,2448 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. Concurrent Request Latency Comparison (1KB &amp; 2KB Random Characters)</t>
+          <t>Concurrent Request Comparison — Single HTTP Request with N Prompts (P50)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Payload Category</t>
+          <t>Payload Size</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L4 P50 (ms)</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TPU v5e P50 (ms)</t>
+          <t>TPU v6e cb460828 (ms)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TPU v6e Megakernel P50 (ms)</t>
+          <t>TPU v5e (ms)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>v6e vs L4 P50</t>
+          <t>L4 GPU (ms)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>v6e vs v5e P50</t>
+          <t>Absolute Delta (v6e vs v5e)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>L4 P99 (ms)</t>
+          <t>% Reduction (v6e vs v5e)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>TPU v5e P99 (ms)</t>
+          <t>Absolute Delta (v6e vs L4)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TPU v6e Megakernel P99 (ms)</t>
+          <t>% Reduction (v6e vs L4)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>v6e vs L4 P99</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>v6e vs v5e P99</t>
+          <t>Faster Setup</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1KB (1024 chars ≈ 1,009 tokens) @ C=1</t>
+          <t>1KB (1024 chars)</t>
         </is>
       </c>
       <c r="B5" s="0">
-        <v>20.7</v>
-      </c>
-      <c r="C5" s="0">
-        <v>11.5</v>
-      </c>
-      <c r="D5" s="0">
-        <v>9.0</v>
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7.4ms</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>11.5ms</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>20.7ms</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-21.7%</t>
-        </is>
-      </c>
-      <c r="G5" s="0">
-        <v>23.5</v>
-      </c>
-      <c r="H5" s="0">
-        <v>12.7</v>
-      </c>
-      <c r="I5" s="0">
-        <v>11.4</v>
+          <t>-4.1ms</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-13.3ms</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>64.3%</t>
+        </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-51.5%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-10.2%</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2KB (2048 chars ≈ 2,016 tokens) @ C=1</t>
+          <t>1KB (1024 chars)</t>
         </is>
       </c>
       <c r="B6" s="0">
-        <v>24.3</v>
-      </c>
-      <c r="C6" s="0">
-        <v>16.5</v>
-      </c>
-      <c r="D6" s="0">
-        <v>11.3</v>
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>17.4ms</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>21.2ms</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-53.5%</t>
+          <t>38.1ms</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-31.5%</t>
-        </is>
-      </c>
-      <c r="G6" s="0">
-        <v>28.2</v>
-      </c>
-      <c r="H6" s="0">
-        <v>17.7</v>
-      </c>
-      <c r="I6" s="0">
-        <v>13.0</v>
+          <t>-3.8ms</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>17.9%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-20.7ms</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>54.3%</t>
+        </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-53.9%</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-26.6%</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1KB (1024 chars ≈ 1,009 tokens) @ C=4</t>
+          <t>1KB (1024 chars)</t>
         </is>
       </c>
       <c r="B7" s="0">
-        <v>38.1</v>
-      </c>
-      <c r="C7" s="0">
-        <v>21.2</v>
-      </c>
-      <c r="D7" s="0">
-        <v>20.5</v>
+        <v>8</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>31.2ms</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>42.5ms</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-46.2%</t>
+          <t>58.7ms</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.3%</t>
-        </is>
-      </c>
-      <c r="G7" s="0">
-        <v>42.9</v>
-      </c>
-      <c r="H7" s="0">
-        <v>22.8</v>
-      </c>
-      <c r="I7" s="0">
-        <v>23.9</v>
+          <t>-11.3ms</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>26.6%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-27.5ms</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>46.8%</t>
+        </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-44.3%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>+4.8%</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2KB (2048 chars ≈ 2,016 tokens) @ C=4</t>
+          <t>1KB (1024 chars)</t>
         </is>
       </c>
       <c r="B8" s="0">
-        <v>52.1</v>
-      </c>
-      <c r="C8" s="0">
-        <v>40.7</v>
-      </c>
-      <c r="D8" s="0">
-        <v>27.4</v>
+        <v>16</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>59.5ms</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>85.4ms</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>96.5ms</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-32.7%</t>
-        </is>
-      </c>
-      <c r="G8" s="0">
-        <v>58.2</v>
-      </c>
-      <c r="H8" s="0">
-        <v>42.8</v>
-      </c>
-      <c r="I8" s="0">
-        <v>32.2</v>
+          <t>-25.9ms</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>30.3%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-37.0ms</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>38.3%</t>
+        </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-44.7%</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>-24.8%</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1KB (1024 chars ≈ 1,009 tokens) @ C=8</t>
+          <t>2KB (2048 chars)</t>
         </is>
       </c>
       <c r="B9" s="0">
-        <v>58.7</v>
-      </c>
-      <c r="C9" s="0">
-        <v>42.5</v>
-      </c>
-      <c r="D9" s="0">
-        <v>31.4</v>
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9.0ms</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>16.5ms</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>24.3ms</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-26.1%</t>
-        </is>
-      </c>
-      <c r="G9" s="0">
-        <v>66.3</v>
-      </c>
-      <c r="H9" s="0">
-        <v>44.5</v>
-      </c>
-      <c r="I9" s="0">
-        <v>37.5</v>
+          <t>-7.5ms</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-15.3ms</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>63.0%</t>
+        </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-43.4%</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>-15.7%</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2KB (2048 chars ≈ 2,016 tokens) @ C=8</t>
+          <t>2KB (2048 chars)</t>
         </is>
       </c>
       <c r="B10" s="0">
-        <v>87.4</v>
-      </c>
-      <c r="C10" s="0">
-        <v>82.6</v>
-      </c>
-      <c r="D10" s="0">
-        <v>50.1</v>
+        <v>4</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>26.6ms</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>40.7ms</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-42.7%</t>
+          <t>52.1ms</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-39.3%</t>
-        </is>
-      </c>
-      <c r="G10" s="0">
-        <v>97.3</v>
-      </c>
-      <c r="H10" s="0">
-        <v>86.0</v>
-      </c>
-      <c r="I10" s="0">
-        <v>54.4</v>
+          <t>-14.1ms</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>34.6%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-25.5ms</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>48.9%</t>
+        </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-44.1%</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-36.7%</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B11" s="0">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>50.1ms</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>82.6ms</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>87.4ms</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-32.5ms</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-37.3ms</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>42.7%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2. RPS Saturation Result (&lt; 50 ms P99 Latency SLA)</t>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B12" s="0">
+        <v>16</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>97.3ms</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>165.9ms</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>156.9ms</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-68.6ms</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>41.4%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-59.6ms</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>38.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Payload Size</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NVIDIA L4 Max RPS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TPU v5e Max RPS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TPU v6e Megakernel Max RPS (max_len=2048)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TPU v6e P50 at Max RPS</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>TPU v6e P99 at Max RPS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>v6e Gain vs L4</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>v6e Gain vs TPU v5e</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1KB (1,024 chars ≈ 1,009 tokens)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>70 RPS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>180 RPS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>280 RPS</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>20.3 ms</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>36.8 ms</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>4.00x (+300.0%)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1.56x (+55.6%)</t>
+          <t>Concurrent Request Comparison — Single HTTP Request with N Prompts (p99)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2KB (2,048 chars ≈ 2,016 tokens)</t>
+          <t>Payload Size</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>40 RPS</t>
+          <t>Concurrency</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>90 RPS</t>
+          <t>TPU v6e cb460828 (ms)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>165 RPS</t>
+          <t>TPU v5e (ms)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15.7 ms</t>
+          <t>L4 GPU (ms)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>42.9 ms</t>
+          <t>Absolute Delta (v6e vs v5e)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4.13x (+312.5%)</t>
+          <t>% Reduction (v6e vs v5e)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.83x (+83.3%)</t>
+          <t>Absolute Delta (v6e vs L4)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>% Reduction (v6e vs L4)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Faster Setup</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B16" s="0">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10.4ms</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>12.7ms</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>23.5ms</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-2.3ms</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-13.1ms</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>55.7%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3. Cost Improvement &amp; Fleet TCO Analysis (OD Pricing: L4 = $0.70/hr, TPU v5e = $1.20/hr, TPU v6e = $2.70/hr)</t>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B17" s="0">
+        <v>4</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>19.4ms</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>22.8ms</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>42.9ms</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-3.4ms</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>14.9%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-23.5ms</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>54.8%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Payload Size</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B18" s="0">
+        <v>8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>On-Demand Price ($/hr)</t>
+          <t>32.7ms</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Max Validated RPS (&lt;50ms P99)</t>
+          <t>44.5ms</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Throughput per Dollar (RPS/$/hr)</t>
+          <t>66.3ms</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Relative Perf/$ vs L4</t>
+          <t>-11.8ms</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cost per Request vs L4</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Effective RPS @ 40% Fleet Util</t>
+          <t>-33.6ms</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chips Needed for 1,000 RPS (@40% Util)</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Monthly Fleet Cost (1,000 RPS @ 40% Util)</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Fleet TCO Summary vs L4</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1KB (1,024 chars)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NVIDIA L4</t>
-        </is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B19" s="0">
+        <v>16</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$0.70</t>
+          <t>60.8ms</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>70 RPS</t>
+          <t>89.9ms</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>100.00 RPS/$</t>
+          <t>107.6ms</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1.00x (Baseline)</t>
+          <t>-29.1ms</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Baseline ($6.94 / 1M req @ 40%)</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>28.0 RPS</t>
-        </is>
-      </c>
-      <c r="I19" s="0">
-        <v>36</v>
+          <t>-46.8ms</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>43.5%</t>
+        </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>$18,396 / mo ($18,250 exact)</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Baseline (36 GPUs)</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1KB (1,024 chars)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cloud TPU v5e (FP32)</t>
-        </is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B20" s="0">
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$1.20</t>
+          <t>10.6ms</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>180 RPS</t>
+          <t>17.7ms</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>150.00 RPS/$</t>
+          <t>28.2ms</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.50x (+50.0%)</t>
+          <t>-7.1ms</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-33.3% Cost / Req ($4.63 / 1M req @ 40%)</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>72.0 RPS</t>
-        </is>
-      </c>
-      <c r="I20" s="0">
-        <v>14</v>
+          <t>-17.6ms</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>62.4%</t>
+        </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>$12,264 / mo ($12,167 exact)</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>-33.3% ($6,132/mo saved, 14 chips)</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1KB (1,024 chars)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Cloud TPU v6e (FP32 Megakernel Optimized, max_len=2048)</t>
-        </is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B21" s="0">
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$2.70</t>
+          <t>29.3ms</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>280 RPS</t>
+          <t>42.8ms</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>103.70 RPS/$</t>
+          <t>58.2ms</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.04x (+3.7% vs L4)</t>
+          <t>-13.5ms</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.6% Cost / Req ($6.70 / 1M req @ 40%)</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>112.0 RPS</t>
-        </is>
-      </c>
-      <c r="I21" s="0">
-        <v>9</v>
+          <t>-28.9ms</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>49.7%</t>
+        </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>$17,739 / mo ($17,600 exact)</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>-3.6% vs L4 ($657/mo saved, 4.0x fewer nodes: 9 vs 36)</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2KB (2,048 chars)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NVIDIA L4</t>
-        </is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B22" s="0">
+        <v>8</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$0.70</t>
+          <t>52.4ms</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>40 RPS</t>
+          <t>86.0ms</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>57.14 RPS/$</t>
+          <t>97.3ms</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.00x (Baseline)</t>
+          <t>-33.6ms</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Baseline ($12.15 / 1M req @ 40%)</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>16.0 RPS</t>
-        </is>
-      </c>
-      <c r="I22" s="0">
-        <v>63</v>
+          <t>-44.9ms</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>46.1%</t>
+        </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>$32,193 / mo ($31,938 exact)</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Baseline (63 GPUs)</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2KB (2,048 chars)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Cloud TPU v5e (FP32)</t>
-        </is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B23" s="0">
+        <v>16</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$1.20</t>
+          <t>104.0ms</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>90 RPS</t>
+          <t>171.2ms</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.00 RPS/$</t>
+          <t>175.5ms</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.31x (+31.3%)</t>
+          <t>-67.2ms</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-23.8% Cost / Req ($9.26 / 1M req @ 40%)</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>36.0 RPS</t>
-        </is>
-      </c>
-      <c r="I23" s="0">
-        <v>28</v>
+          <t>-71.5ms</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>$24,528 / mo ($24,333 exact)</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>-23.8% ($7,665/mo saved, 28 chips)</t>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2KB (2,048 chars)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Cloud TPU v6e (FP32 Megakernel Optimized, max_len=2048)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>$2.70</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>165 RPS</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>61.11 RPS/$</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1.07x (+7.0% vs L4)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-6.5% Cost / Req ($11.36 / 1M req @ 40%)</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>66.0 RPS</t>
-        </is>
-      </c>
-      <c r="I24" s="0">
-        <v>16</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>$31,536 / mo ($29,864 exact)</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>-6.5% exact (-2.0% fleet, $657/mo saved, 3.94x fewer nodes: 16 vs 63)</t>
-        </is>
-      </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Concurrent Request Comparison — k6 Concurrent HTTP Requests VUS=1,4,8,16 (P50)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4. Regional Availability (GCP Americas, Europe, Asia-Pacific)</t>
+          <t>Payload Size</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Concurrency</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TPU v6e cb460828 (ms)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TPU v5e (ms)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>L4 GPU (ms)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Absolute Delta (v6e vs v5e)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>% Reduction (v6e vs v5e)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Absolute Delta (v6e vs L4)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>% Reduction (v6e vs L4)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Faster Setup</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Accelerator</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Americas Regions</t>
-        </is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B27" s="0">
+        <v>1</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe Regions</t>
+          <t>6.9ms</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Asia-Pacific Regions</t>
+          <t>11.5ms</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>20.7ms</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-4.6ms</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-13.8ms</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NVIDIA L4 (g2)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>us-central1, us-east1, us-east4, us-west1, us-west4, northamerica-northeast1, southamerica-east1</t>
-        </is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B28" s="0">
+        <v>4</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>europe-west1, europe-west2, europe-west3, europe-west4, europe-north1</t>
+          <t>9.9ms</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>asia-east1, asia-northeast1, asia-northeast3, asia-south1, asia-southeast1, australia-southeast1</t>
+          <t>21.2ms</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>38.1ms</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-11.3ms</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-28.2ms</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>74.0%</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud TPU v5e</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>us-central1, us-east1, us-west1, us-west4, southamerica-west1</t>
-        </is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B29" s="0">
+        <v>8</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>europe-west4</t>
+          <t>14.8ms</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>asia-east1, asia-northeast1</t>
+          <t>42.5ms</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>58.7ms</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-27.7ms</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>65.2%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-43.9ms</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>74.8%</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud TPU v6e (Trillium)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>us-central1, us-east1, us-east5, us-south1, us-west4, southamerica-west1</t>
-        </is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B30" s="0">
+        <v>16</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>europe-west4</t>
+          <t>30.1ms</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>asia-east1, asia-northeast1</t>
+          <t>85.4ms</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>96.5ms</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-55.3ms</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>64.8%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-66.4ms</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B31" s="0">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>8.6ms</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>16.5ms</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>24.3ms</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-7.9ms</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>47.9%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-15.7ms</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>64.6%</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B32" s="0">
+        <v>4</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>12.4ms</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>40.7ms</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>52.1ms</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-28.3ms</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>69.5%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-39.7ms</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>76.2%</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B33" s="0">
+        <v>8</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20.1ms</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>82.6ms</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>87.4ms</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-62.5ms</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>75.7%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-67.3ms</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>77.0%</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B34" s="0">
+        <v>16</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>42.0ms</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>165.9ms</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>156.9ms</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-123.9ms</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>74.7%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-114.9ms</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>73.2%</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Concurrent Request Comparison — k6 Concurrent HTTP Requests VUS=1,4,8,16 (p99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Payload Size</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Concurrency</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TPU v6e cb460828 (ms)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TPU v5e (ms)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>L4 GPU (ms)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Absolute Delta (v6e vs v5e)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>% Reduction (v6e vs v5e)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Absolute Delta (v6e vs L4)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>% Reduction (v6e vs L4)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Faster Setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B38" s="0">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>8.0ms</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>12.7ms</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>23.5ms</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-4.7ms</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>37.0%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-15.5ms</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>66.0%</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B39" s="0">
+        <v>4</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>12.3ms</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>22.8ms</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>42.9ms</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-10.5ms</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>46.1%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-30.6ms</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>71.3%</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B40" s="0">
+        <v>8</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20.2ms</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>44.5ms</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>66.3ms</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-24.3ms</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>54.6%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-46.1ms</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>69.5%</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1KB (1024 chars)</t>
+        </is>
+      </c>
+      <c r="B41" s="0">
+        <v>16</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>39.3ms</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>89.9ms</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>107.6ms</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-50.6ms</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>56.3%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-68.3ms</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>63.5%</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B42" s="0">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>9.5ms</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>17.7ms</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>28.2ms</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-8.2ms</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>46.3%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-18.7ms</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>66.3%</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B43" s="0">
+        <v>4</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>16.2ms</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>42.8ms</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>58.2ms</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-26.6ms</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>62.1%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-42.0ms</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>72.2%</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B44" s="0">
+        <v>8</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>26.8ms</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>86.0ms</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>97.3ms</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-59.2ms</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-70.5ms</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>72.5%</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2KB (2048 chars)</t>
+        </is>
+      </c>
+      <c r="B45" s="0">
+        <v>16</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>50.0ms</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>171.2ms</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>175.5ms</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-121.2ms</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>70.8%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-125.5ms</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>71.5%</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>TPU v6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>RPS Saturation Result (p99 &lt; 50 ms SLA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Payload</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>RPS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>p50</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>p99</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>RPS Improvement (vs L4 GPU)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>RPS Improvement (vs TPU v5e)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>L4 GPU</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>70/s</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TPU v5e</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>180/s (187/s max achieved)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>19.9ms</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>29.6ms</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>+157.1%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>TPU v6e (Opus Megakernel cb460828, 10-RPS grid)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>490/s</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>14.1ms</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>46.3ms</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>+600.0% (7.00x)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>+172.2% vs 180/s (+162.0% vs 187/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TPU v6e (Opus Megakernel cb460828, 20-RPS grid)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>480/s</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>12.6ms</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>27.9ms</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>+585.7% (6.86x)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>+166.7% vs 180/s (+156.7% vs 187/s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>L4 GPU</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>40/s</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>TPU v5e</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>90/s</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>17.2ms</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>26.5ms</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>+125.0%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>TPU v6e (Opus Megakernel cb460828, max PASS)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>320/s</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>12.6ms</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>25.3ms</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>+700.0% (8.00x)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>+255.6% (3.56x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2K</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>TPU v6e (Opus Megakernel cb460828, 300 RPS target)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>300/s</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>12.9ms</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>18.6ms</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>+650.0% (7.50x)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>+233.3% (3.33x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Cost Improvement (Matching Zhemin's Formula: Hourly Cost / (0.40 * Max RPS * 3600) * 1,000,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Machine Type</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Machine Config</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Hourly Cost</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Cost per 1M request (1K Payload)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Cost per 1M request (2K Payload)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>g2-standard-4</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>L4 GPUs: 1 | vCPUs: 4 | Memory: 16GiB | GPU Memory: 24GiB</t>
+        </is>
+      </c>
+      <c r="C60" s="0">
+        <v>0.7</v>
+      </c>
+      <c r="D60" s="0">
+        <v>6.944444444</v>
+      </c>
+      <c r="E60" s="0">
+        <v>12.15277778</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ct5lp-hightpu-1t (Zhemin sheet $1.20, 187/90 RPS)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>vCPUs: 24 | Memory: 48 GB | TPU HBM: 16 GB</t>
+        </is>
+      </c>
+      <c r="C61" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="D61" s="0">
+        <v>4.456327986</v>
+      </c>
+      <c r="E61" s="0">
+        <v>9.259259259</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ct5lp-hightpu-1t (OD $1.22, 187/90 RPS)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>vCPUs: 24 | Memory: 48 GB | TPU HBM: 16 GB</t>
+        </is>
+      </c>
+      <c r="C62" s="0">
+        <v>1.22</v>
+      </c>
+      <c r="D62" s="0">
+        <v>4.530600119</v>
+      </c>
+      <c r="E62" s="0">
+        <v>9.413580247</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ct5lp-hightpu-1t (OD $1.22, SLA-passing 180/90 RPS)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>vCPUs: 24 | Memory: 48 GB | TPU HBM: 16 GB</t>
+        </is>
+      </c>
+      <c r="C63" s="0">
+        <v>1.22</v>
+      </c>
+      <c r="D63" s="0">
+        <v>4.706790123</v>
+      </c>
+      <c r="E63" s="0">
+        <v>9.413580247</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ct6e-standard-1t (Opus Megakernel cb460828, 490/320 RPS max PASS)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>TPU v6e: 1 chip | vCPUs: 44 | Memory: 176 GB | TPU HBM: 32 GB</t>
+        </is>
+      </c>
+      <c r="C64" s="0">
+        <v>2.7</v>
+      </c>
+      <c r="D64" s="0">
+        <v>3.826530612</v>
+      </c>
+      <c r="E64" s="0">
+        <v>5.859375</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ct6e-standard-1t (Opus Megakernel cb460828, 480/320 RPS 20-RPS grid)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>TPU v6e: 1 chip | vCPUs: 44 | Memory: 176 GB | TPU HBM: 32 GB</t>
+        </is>
+      </c>
+      <c r="C65" s="0">
+        <v>2.7</v>
+      </c>
+      <c r="D65" s="0">
+        <v>3.90625</v>
+      </c>
+      <c r="E65" s="0">
+        <v>5.859375</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cost Improvement (v5e $1.20 vs L4 $0.70 — Zhemin Baseline)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>35.83% reduction</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>23.81% reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cost Improvement (v6e $2.70 vs L4 $0.70 — 490 / 320 RPS)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>44.90% reduction</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>51.79% reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cost Improvement (v6e $2.70 vs L4 $0.70 — 480 / 320 RPS)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>43.75% reduction</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>51.79% reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cost Improvement (v6e $2.70 vs v5e $1.20 @ 187/90 RPS — 490/320 RPS)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>14.13% reduction</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>36.72% reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cost Improvement (v6e $2.70 vs v5e $1.22 @ 187/90 RPS — 490/320 RPS)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>15.54% reduction</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>37.76% reduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Cost Improvement (v6e $2.70 vs v5e $1.22 @ 180/90 RPS — 490/320 RPS)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>18.70% reduction</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>37.76% reduction</t>
         </is>
       </c>
     </row>
